--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -892,25 +892,25 @@
         <v>31</v>
       </c>
       <c r="E13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H13" s="1">
-        <v>29.03</v>
+        <v>22.58</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1791,25 +1791,25 @@
         <v>31</v>
       </c>
       <c r="E13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H13" s="1">
-        <v>29.03</v>
+        <v>22.58</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -691,22 +691,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -758,22 +761,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>5.26</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -825,22 +831,25 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9.1</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1590,22 +1599,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1657,22 +1669,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>5.26</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1724,22 +1739,25 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9.1</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -548,28 +548,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>26</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="H3" s="1">
-        <v>10.34</v>
+        <v>13.33</v>
       </c>
       <c r="I3" s="2">
         <v>8.1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -863,22 +863,22 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="H12" s="1">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="I12" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1017,13 +1017,13 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1305,13 +1305,13 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1456,28 +1456,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>26</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="H3" s="1">
-        <v>10.34</v>
+        <v>13.33</v>
       </c>
       <c r="I3" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1771,22 +1771,22 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="H12" s="1">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
       <c r="I12" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="27">
   <si>
     <t>Docente</t>
   </si>
@@ -54,12 +54,15 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
     <t>2ARHV</t>
   </si>
   <si>
@@ -90,10 +93,10 @@
     <t>DETERMINA REMUNERACIONES DEL PERSONAL EN SITUACIONES EXTRAORDINARIAS</t>
   </si>
   <si>
+    <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
+  </si>
+  <si>
     <t>DISTINGUE LOS DIFERENTES TIPOS DE EMPRESA POR SU GIRO, ÁREAS FUNCIONALES, DOCUMENTACIÓN ADMINISTRATIVA Y RECURSOS</t>
-  </si>
-  <si>
-    <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
   </si>
 </sst>
 </file>
@@ -507,10 +510,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>33</v>
@@ -542,10 +545,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -577,10 +580,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>36</v>
@@ -612,10 +615,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -647,28 +650,28 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>40</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="H6" s="1">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -682,28 +685,28 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>95</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>5</v>
+        <v>5.26</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -717,28 +720,28 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>87.88</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -749,31 +752,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>94.73999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="H9" s="1">
-        <v>5.26</v>
+        <v>6.67</v>
       </c>
       <c r="I9" s="2">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -784,31 +787,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>78.95</v>
+        <v>77.42</v>
       </c>
       <c r="H10" s="1">
-        <v>21.05</v>
+        <v>22.58</v>
       </c>
       <c r="I10" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -819,31 +822,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I11" s="2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -854,31 +857,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>93.33</v>
+        <v>87.88</v>
       </c>
       <c r="H12" s="1">
-        <v>6.67</v>
+        <v>12.12</v>
       </c>
       <c r="I12" s="2">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -889,31 +892,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>77.42</v>
+        <v>78.95</v>
       </c>
       <c r="H13" s="1">
-        <v>22.58</v>
+        <v>21.05</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -979,10 +982,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>33</v>
@@ -1011,10 +1014,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -1043,10 +1046,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>36</v>
@@ -1075,10 +1078,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -1107,10 +1110,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>40</v>
@@ -1139,19 +1142,19 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1160,7 +1163,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1171,19 +1174,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1192,7 +1195,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1200,22 +1203,22 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1224,7 +1227,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1232,22 +1235,22 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1256,7 +1259,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1264,22 +1267,22 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1288,7 +1291,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1296,22 +1299,22 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1320,7 +1323,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1328,22 +1331,22 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1352,7 +1355,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1415,10 +1418,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
         <v>33</v>
@@ -1450,10 +1453,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -1485,10 +1488,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>36</v>
@@ -1520,10 +1523,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -1555,28 +1558,28 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>40</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="H6" s="1">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1590,28 +1593,28 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>95</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>5</v>
+        <v>5.26</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1625,28 +1628,28 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>87.88</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1657,31 +1660,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>94.73999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="H9" s="1">
-        <v>5.26</v>
+        <v>6.67</v>
       </c>
       <c r="I9" s="2">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1692,31 +1695,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>78.95</v>
+        <v>77.42</v>
       </c>
       <c r="H10" s="1">
-        <v>21.05</v>
+        <v>22.58</v>
       </c>
       <c r="I10" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1727,31 +1730,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I11" s="2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1762,31 +1765,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>93.33</v>
+        <v>87.88</v>
       </c>
       <c r="H12" s="1">
-        <v>6.67</v>
+        <v>12.12</v>
       </c>
       <c r="I12" s="2">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1797,31 +1800,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>77.42</v>
+        <v>78.95</v>
       </c>
       <c r="H13" s="1">
-        <v>22.58</v>
+        <v>21.05</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J13">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="28">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Camacho Juárez Sergio Eduardo</t>
@@ -63,6 +62,27 @@
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>ELABORA ESTRATEGIAS PARA REALIZAR LAS ACTIVIDADES DE SU ÁREA</t>
+  </si>
+  <si>
+    <t>ASISTE EN LAS ACTIVIDADES DE CAPACITACIÓN PARA EL DESARROLLO DEL CAPITAL HUMANO</t>
+  </si>
+  <si>
+    <t>DETERMINA LA NÓMINA DEL PERSONAL DE LA ORGANIZACIÓN TOMANDO EN CUENTA LA NORMATIVIDAD LABORAL</t>
+  </si>
+  <si>
+    <t>DETERMINA REMUNERACIONES DEL PERSONAL EN SITUACIONES EXTRAORDINARIAS</t>
+  </si>
+  <si>
+    <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
+  </si>
+  <si>
+    <t>DISTINGUE LOS DIFERENTES TIPOS DE EMPRESA POR SU GIRO, ÁREAS FUNCIONALES, DOCUMENTACIÓN ADMINISTRATIVA Y RECURSOS</t>
+  </si>
+  <si>
     <t>2ARHV</t>
   </si>
   <si>
@@ -79,24 +99,6 @@
   </si>
   <si>
     <t>4ARHM</t>
-  </si>
-  <si>
-    <t>ELABORA ESTRATEGIAS PARA REALIZAR LAS ACTIVIDADES DE SU ÁREA</t>
-  </si>
-  <si>
-    <t>ASISTE EN LAS ACTIVIDADES DE CAPACITACIÓN PARA EL DESARROLLO DEL CAPITAL HUMANO</t>
-  </si>
-  <si>
-    <t>DETERMINA LA NÓMINA DEL PERSONAL DE LA ORGANIZACIÓN TOMANDO EN CUENTA LA NORMATIVIDAD LABORAL</t>
-  </si>
-  <si>
-    <t>DETERMINA REMUNERACIONES DEL PERSONAL EN SITUACIONES EXTRAORDINARIAS</t>
-  </si>
-  <si>
-    <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
-  </si>
-  <si>
-    <t>DISTINGUE LOS DIFERENTES TIPOS DE EMPRESA POR SU GIRO, ÁREAS FUNCIONALES, DOCUMENTACIÓN ADMINISTRATIVA Y RECURSOS</t>
   </si>
 </sst>
 </file>
@@ -460,11 +462,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -510,10 +512,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2">
         <v>33</v>
@@ -525,10 +527,10 @@
         <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>90.91</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
       <c r="I2" s="2">
         <v>7.8</v>
@@ -545,10 +547,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -560,10 +562,10 @@
         <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>86.67</v>
+        <v>86.7</v>
       </c>
       <c r="H3" s="1">
-        <v>13.33</v>
+        <v>13.3</v>
       </c>
       <c r="I3" s="2">
         <v>8.1</v>
@@ -580,10 +582,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>36</v>
@@ -595,10 +597,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>97.22</v>
+        <v>97.2</v>
       </c>
       <c r="H4" s="1">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I4" s="2">
         <v>9.1</v>
@@ -615,10 +617,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -630,10 +632,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>90.31999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="H5" s="1">
-        <v>9.68</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5" s="2">
         <v>8.800000000000001</v>
@@ -647,37 +649,31 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>95</v>
+        <v>91.5</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -685,28 +681,28 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
         <v>38</v>
-      </c>
-      <c r="E7">
-        <v>36</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="H7" s="1">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="I7" s="2">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -723,25 +719,25 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>36</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>100</v>
+        <v>94.7</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I8" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -752,31 +748,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -787,31 +783,25 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>77.42</v>
+        <v>96.5</v>
       </c>
       <c r="H10" s="1">
-        <v>22.58</v>
+        <v>3.5</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -822,31 +812,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="H11" s="1">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I11" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -857,31 +847,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>87.88</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>12.12</v>
+        <v>22.6</v>
       </c>
       <c r="I12" s="2">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -892,37 +882,194 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>61</v>
+      </c>
+      <c r="E13">
+        <v>52</v>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+      <c r="G13" s="1">
+        <v>85.2</v>
+      </c>
+      <c r="H13" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14">
+        <v>40</v>
+      </c>
+      <c r="E14">
+        <v>37</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1">
+        <v>92.5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>33</v>
+      </c>
+      <c r="E15">
+        <v>29</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="H15" s="1">
+        <v>12.1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13">
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16">
         <v>38</v>
       </c>
-      <c r="E13">
+      <c r="E16">
         <v>30</v>
       </c>
-      <c r="F13">
+      <c r="F16">
         <v>8</v>
       </c>
-      <c r="G13" s="1">
-        <v>78.95</v>
-      </c>
-      <c r="H13" s="1">
-        <v>21.05</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="G16" s="1">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>21.1</v>
+      </c>
+      <c r="I16" s="2">
         <v>7.5</v>
       </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17">
+        <v>111</v>
+      </c>
+      <c r="E17">
+        <v>96</v>
+      </c>
+      <c r="F17">
+        <v>15</v>
+      </c>
+      <c r="G17" s="1">
+        <v>86.5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18">
+        <v>416</v>
+      </c>
+      <c r="E18">
+        <v>377</v>
+      </c>
+      <c r="F18">
+        <v>39</v>
+      </c>
+      <c r="G18" s="1">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="H18" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -932,11 +1079,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -982,31 +1129,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2">
         <v>33</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>9.1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1014,31 +1164,34 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>13.3</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1046,31 +1199,34 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>2.8</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9.1</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1078,63 +1234,63 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>90.3</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F6">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>91.5</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>8.5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.5</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1142,31 +1298,34 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
         <v>38</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
       <c r="F7">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1177,660 +1336,357 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8">
+        <v>38</v>
+      </c>
+      <c r="E8">
         <v>36</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
       <c r="F8">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>5.3</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9.1</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>96.5</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>3.5</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>6.7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>22.6</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>61</v>
+      </c>
+      <c r="E13">
+        <v>52</v>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+      <c r="G13" s="1">
+        <v>85.2</v>
+      </c>
+      <c r="H13" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14">
+        <v>40</v>
+      </c>
+      <c r="E14">
+        <v>37</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1">
+        <v>92.5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>33</v>
+      </c>
+      <c r="E15">
+        <v>29</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="H15" s="1">
+        <v>12.1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13">
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16">
         <v>38</v>
       </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>38</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>100</v>
-      </c>
-      <c r="J13">
-        <v>38</v>
-      </c>
-      <c r="K13" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="E16">
+        <v>30</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16" s="1">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>21.1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17">
+        <v>111</v>
+      </c>
+      <c r="E17">
+        <v>96</v>
+      </c>
+      <c r="F17">
+        <v>15</v>
+      </c>
+      <c r="G17" s="1">
+        <v>86.5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18">
+        <v>416</v>
+      </c>
+      <c r="E18">
+        <v>377</v>
+      </c>
+      <c r="F18">
+        <v>39</v>
+      </c>
+      <c r="G18" s="1">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="H18" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J18">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2">
-        <v>33</v>
-      </c>
-      <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1">
-        <v>90.91</v>
-      </c>
-      <c r="H2" s="1">
-        <v>9.09</v>
-      </c>
-      <c r="I2" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
-      </c>
-      <c r="E3">
-        <v>26</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3" s="1">
-        <v>86.67</v>
-      </c>
-      <c r="H3" s="1">
-        <v>13.33</v>
-      </c>
-      <c r="I3" s="2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4">
-        <v>36</v>
-      </c>
-      <c r="E4">
-        <v>35</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>97.22</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2.78</v>
-      </c>
-      <c r="I4" s="2">
-        <v>9.1</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5">
-        <v>31</v>
-      </c>
-      <c r="E5">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1">
-        <v>90.31999999999999</v>
-      </c>
-      <c r="H5" s="1">
-        <v>9.68</v>
-      </c>
-      <c r="I5" s="2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>40</v>
-      </c>
-      <c r="E6">
-        <v>38</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>95</v>
-      </c>
-      <c r="H6" s="1">
-        <v>5</v>
-      </c>
-      <c r="I6" s="2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>38</v>
-      </c>
-      <c r="E7">
-        <v>36</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="H7" s="1">
-        <v>5.26</v>
-      </c>
-      <c r="I7" s="2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8">
-        <v>36</v>
-      </c>
-      <c r="E8">
-        <v>36</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>100</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>9.1</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9">
-        <v>30</v>
-      </c>
-      <c r="E9">
-        <v>28</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1">
-        <v>93.33</v>
-      </c>
-      <c r="H9" s="1">
-        <v>6.67</v>
-      </c>
-      <c r="I9" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10">
-        <v>31</v>
-      </c>
-      <c r="E10">
-        <v>24</v>
-      </c>
-      <c r="F10">
-        <v>7</v>
-      </c>
-      <c r="G10" s="1">
-        <v>77.42</v>
-      </c>
-      <c r="H10" s="1">
-        <v>22.58</v>
-      </c>
-      <c r="I10" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11">
-        <v>40</v>
-      </c>
-      <c r="E11">
-        <v>37</v>
-      </c>
-      <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1">
-        <v>92.5</v>
-      </c>
-      <c r="H11" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="I11" s="2">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12">
-        <v>33</v>
-      </c>
-      <c r="E12">
-        <v>29</v>
-      </c>
-      <c r="F12">
-        <v>4</v>
-      </c>
-      <c r="G12" s="1">
-        <v>87.88</v>
-      </c>
-      <c r="H12" s="1">
-        <v>12.12</v>
-      </c>
-      <c r="I12" s="2">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13">
-        <v>38</v>
-      </c>
-      <c r="E13">
-        <v>30</v>
-      </c>
-      <c r="F13">
-        <v>8</v>
-      </c>
-      <c r="G13" s="1">
-        <v>78.95</v>
-      </c>
-      <c r="H13" s="1">
-        <v>21.05</v>
-      </c>
-      <c r="I13" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
+      <c r="K18" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="29">
   <si>
     <t>Docente</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>ELABORA ESTRATEGIAS PARA REALIZAR LAS ACTIVIDADES DE SU ÁREA</t>
   </si>
   <si>
@@ -77,10 +74,16 @@
     <t>DETERMINA REMUNERACIONES DEL PERSONAL EN SITUACIONES EXTRAORDINARIAS</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
   </si>
   <si>
     <t>DISTINGUE LOS DIFERENTES TIPOS DE EMPRESA POR SU GIRO, ÁREAS FUNCIONALES, DOCUMENTACIÓN ADMINISTRATIVA Y RECURSOS</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>2ARHV</t>
@@ -466,7 +469,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -512,10 +515,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>33</v>
@@ -547,10 +550,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -582,10 +585,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>36</v>
@@ -617,10 +620,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -651,6 +654,9 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
       <c r="D6">
         <v>130</v>
       </c>
@@ -681,10 +687,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -716,10 +722,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>38</v>
@@ -751,10 +757,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>36</v>
@@ -785,6 +791,9 @@
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
       <c r="D10">
         <v>114</v>
       </c>
@@ -818,7 +827,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>30</v>
@@ -850,10 +859,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>31</v>
@@ -884,6 +893,9 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
       <c r="D13">
         <v>61</v>
       </c>
@@ -917,7 +929,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>40</v>
@@ -952,7 +964,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>33</v>
@@ -987,7 +999,7 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>38</v>
@@ -1018,6 +1030,9 @@
       <c r="A17" t="s">
         <v>14</v>
       </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
       <c r="D17">
         <v>111</v>
       </c>
@@ -1044,8 +1059,8 @@
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>15</v>
+      <c r="B18" t="s">
+        <v>22</v>
       </c>
       <c r="D18">
         <v>416</v>
@@ -1129,10 +1144,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>33</v>
@@ -1164,10 +1179,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -1199,10 +1214,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>36</v>
@@ -1234,10 +1249,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>31</v>
@@ -1268,6 +1283,9 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
       <c r="D6">
         <v>130</v>
       </c>
@@ -1298,10 +1316,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -1333,10 +1351,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>38</v>
@@ -1368,10 +1386,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>36</v>
@@ -1402,6 +1420,9 @@
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
       <c r="D10">
         <v>114</v>
       </c>
@@ -1435,7 +1456,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>30</v>
@@ -1467,10 +1488,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>31</v>
@@ -1501,6 +1522,9 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
       <c r="D13">
         <v>61</v>
       </c>
@@ -1534,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>40</v>
@@ -1569,7 +1593,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>33</v>
@@ -1604,7 +1628,7 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>38</v>
@@ -1635,6 +1659,9 @@
       <c r="A17" t="s">
         <v>14</v>
       </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
       <c r="D17">
         <v>111</v>
       </c>
@@ -1661,8 +1688,8 @@
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>15</v>
+      <c r="B18" t="s">
+        <v>22</v>
       </c>
       <c r="D18">
         <v>416</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="29">
   <si>
     <t>Docente</t>
   </si>
@@ -1153,6 +1154,635 @@
         <v>33</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>33</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>36</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>36</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>31</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>31</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>130</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>130</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>130</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>40</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>38</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>38</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>38</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>36</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>36</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>114</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>114</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>114</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>30</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12">
+        <v>31</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>31</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>31</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>61</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>61</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>61</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14">
+        <v>40</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>40</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>40</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15">
+        <v>33</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>33</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>33</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16">
+        <v>38</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>38</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17">
+        <v>111</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>111</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>111</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18">
+        <v>416</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>416</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>416</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2">
+        <v>33</v>
+      </c>
+      <c r="E2">
         <v>30</v>
       </c>
       <c r="F2">

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -522,28 +522,28 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>30</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>90.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H2" s="1">
-        <v>9.1</v>
+        <v>11.8</v>
       </c>
       <c r="I2" s="2">
         <v>7.8</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -659,28 +659,28 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6">
         <v>119</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>91.5</v>
+        <v>90.8</v>
       </c>
       <c r="H6" s="1">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6" s="2">
         <v>8.4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -968,19 +968,19 @@
         <v>23</v>
       </c>
       <c r="D15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15">
         <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H15" s="1">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="I15" s="2">
         <v>8.699999999999999</v>
@@ -1035,19 +1035,19 @@
         <v>19</v>
       </c>
       <c r="D17">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E17">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F17">
         <v>15</v>
       </c>
       <c r="G17" s="1">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="I17" s="2">
         <v>8.199999999999999</v>
@@ -1064,28 +1064,28 @@
         <v>22</v>
       </c>
       <c r="D18">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E18">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F18">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G18" s="1">
-        <v>90.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I18" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1151,13 +1151,13 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -1288,13 +1288,13 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1463,25 +1463,25 @@
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1498,25 +1498,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1530,25 +1530,25 @@
         <v>61</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F13">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1565,25 +1565,25 @@
         <v>40</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F14">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>7.5</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1597,28 +1597,28 @@
         <v>23</v>
       </c>
       <c r="D15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>11.8</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J15">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1635,25 +1635,25 @@
         <v>38</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F16">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1664,28 +1664,28 @@
         <v>19</v>
       </c>
       <c r="D17">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F17">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>13.4</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1693,28 +1693,28 @@
         <v>22</v>
       </c>
       <c r="D18">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="F18">
-        <v>416</v>
+        <v>271</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>35.2</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>64.8</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J18">
-        <v>416</v>
+        <v>245</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>58.6</v>
       </c>
     </row>
   </sheetData>
@@ -1780,28 +1780,28 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>30</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>90.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H2" s="1">
-        <v>9.1</v>
+        <v>11.8</v>
       </c>
       <c r="I2" s="2">
         <v>7.9</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1917,28 +1917,28 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6">
         <v>119</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>91.5</v>
+        <v>90.8</v>
       </c>
       <c r="H6" s="1">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6" s="2">
         <v>8.5</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2092,19 +2092,19 @@
         <v>30</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>93.3</v>
+        <v>80</v>
       </c>
       <c r="H11" s="1">
-        <v>6.7</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2127,19 +2127,19 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>77.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>22.6</v>
+        <v>16.1</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2159,16 +2159,16 @@
         <v>61</v>
       </c>
       <c r="E13">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>85.2</v>
+        <v>82</v>
       </c>
       <c r="H13" s="1">
-        <v>14.8</v>
+        <v>18</v>
       </c>
       <c r="I13" s="2">
         <v>7.6</v>
@@ -2206,7 +2206,7 @@
         <v>7.5</v>
       </c>
       <c r="I14" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2226,22 +2226,22 @@
         <v>23</v>
       </c>
       <c r="D15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15">
         <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H15" s="1">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="I15" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>21.1</v>
       </c>
       <c r="I16" s="2">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2293,22 +2293,22 @@
         <v>19</v>
       </c>
       <c r="D17">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E17">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F17">
         <v>15</v>
       </c>
       <c r="G17" s="1">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="I17" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2322,28 +2322,28 @@
         <v>22</v>
       </c>
       <c r="D18">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E18">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F18">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G18" s="1">
-        <v>90.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="H18" s="1">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -525,25 +525,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="H2" s="1">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -572,13 +572,13 @@
         <v>13.3</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -662,25 +662,25 @@
         <v>131</v>
       </c>
       <c r="E6">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>90.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I6" s="2">
         <v>8.4</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1067,25 +1067,25 @@
         <v>418</v>
       </c>
       <c r="E18">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F18">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18" s="1">
-        <v>90.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H18" s="1">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I18" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1154,25 +1154,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>11.8</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1189,25 +1189,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1224,25 +1224,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1259,25 +1259,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>90.3</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1291,25 +1291,25 @@
         <v>131</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F6">
-        <v>131</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>90.8</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1696,25 +1696,25 @@
         <v>418</v>
       </c>
       <c r="E18">
-        <v>147</v>
+        <v>266</v>
       </c>
       <c r="F18">
-        <v>271</v>
+        <v>152</v>
       </c>
       <c r="G18" s="1">
-        <v>35.2</v>
+        <v>63.6</v>
       </c>
       <c r="H18" s="1">
-        <v>64.8</v>
+        <v>36.4</v>
       </c>
       <c r="I18" s="2">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="J18">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="K18" s="1">
-        <v>58.6</v>
+        <v>27.3</v>
       </c>
     </row>
   </sheetData>
@@ -1795,13 +1795,13 @@
         <v>11.8</v>
       </c>
       <c r="I2" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1818,25 +1818,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="H3" s="1">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1853,16 +1853,16 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>9.1</v>
@@ -1900,7 +1900,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I6" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2337,13 +2337,13 @@
         <v>10</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -1326,25 +1326,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1361,25 +1361,25 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>13.2</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1428,25 +1428,25 @@
         <v>114</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F10">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>62.3</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>37.7</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J10">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1696,25 +1696,25 @@
         <v>418</v>
       </c>
       <c r="E18">
-        <v>266</v>
+        <v>337</v>
       </c>
       <c r="F18">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="G18" s="1">
-        <v>63.6</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>36.4</v>
+        <v>19.4</v>
       </c>
       <c r="I18" s="2">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="J18">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="K18" s="1">
-        <v>27.3</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1967,7 +1967,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1990,16 +1990,16 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>94.7</v>
+        <v>89.5</v>
       </c>
       <c r="H8" s="1">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="I8" s="2">
         <v>9.199999999999999</v>
@@ -2057,19 +2057,19 @@
         <v>114</v>
       </c>
       <c r="E10">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>96.5</v>
+        <v>94.7</v>
       </c>
       <c r="H10" s="1">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="I10" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2325,19 +2325,19 @@
         <v>418</v>
       </c>
       <c r="E18">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F18">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G18" s="1">
-        <v>90</v>
+        <v>89.5</v>
       </c>
       <c r="H18" s="1">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I18" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -1361,25 +1361,25 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>86.8</v>
+        <v>89.5</v>
       </c>
       <c r="H8" s="1">
-        <v>13.2</v>
+        <v>10.5</v>
       </c>
       <c r="I8" s="2">
         <v>8.9</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>2.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1396,25 +1396,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1428,25 +1428,25 @@
         <v>114</v>
       </c>
       <c r="E10">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="F10">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>62.3</v>
+        <v>94.7</v>
       </c>
       <c r="H10" s="1">
-        <v>37.7</v>
+        <v>5.3</v>
       </c>
       <c r="I10" s="2">
-        <v>5.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>32.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1696,25 +1696,25 @@
         <v>418</v>
       </c>
       <c r="E18">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="F18">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="G18" s="1">
-        <v>80.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="H18" s="1">
-        <v>19.4</v>
+        <v>10.5</v>
       </c>
       <c r="I18" s="2">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>8.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -1098,8 +1098,7 @@
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1727,8 +1726,7 @@
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1818,19 +1816,19 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>83.3</v>
+        <v>76.7</v>
       </c>
       <c r="H3" s="1">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="I3" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1865,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1888,19 +1886,19 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>90.3</v>
+        <v>96.8</v>
       </c>
       <c r="H5" s="1">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1932,7 +1930,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2037,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2104,7 +2102,7 @@
         <v>20</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2127,19 +2125,19 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>83.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="H12" s="1">
-        <v>16.1</v>
+        <v>3.2</v>
       </c>
       <c r="I12" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2159,19 +2157,19 @@
         <v>61</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>82</v>
+        <v>88.5</v>
       </c>
       <c r="H13" s="1">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="I13" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2206,7 +2204,7 @@
         <v>7.5</v>
       </c>
       <c r="I14" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2264,16 +2262,16 @@
         <v>38</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>78.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="H16" s="1">
-        <v>21.1</v>
+        <v>13.2</v>
       </c>
       <c r="I16" s="2">
         <v>8.199999999999999</v>
@@ -2296,19 +2294,19 @@
         <v>112</v>
       </c>
       <c r="E17">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1">
-        <v>86.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="H17" s="1">
-        <v>13.4</v>
+        <v>10.7</v>
       </c>
       <c r="I17" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2325,19 +2323,19 @@
         <v>418</v>
       </c>
       <c r="E18">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F18">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G18" s="1">
-        <v>89.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -1965,7 +1965,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1988,19 +1988,19 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>89.5</v>
+        <v>86.8</v>
       </c>
       <c r="H8" s="1">
-        <v>10.5</v>
+        <v>13.2</v>
       </c>
       <c r="I8" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2055,19 +2055,19 @@
         <v>114</v>
       </c>
       <c r="E10">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>94.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="I10" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2323,16 +2323,16 @@
         <v>418</v>
       </c>
       <c r="E18">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F18">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G18" s="1">
-        <v>91.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="I18" s="2">
         <v>8.199999999999999</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20222.xlsx
@@ -2125,16 +2125,16 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>7.2</v>
@@ -2157,16 +2157,16 @@
         <v>61</v>
       </c>
       <c r="E13">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>88.5</v>
+        <v>90.2</v>
       </c>
       <c r="H13" s="1">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I13" s="2">
         <v>7.3</v>
@@ -2323,16 +2323,16 @@
         <v>418</v>
       </c>
       <c r="E18">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F18">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" s="1">
-        <v>90.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="I18" s="2">
         <v>8.199999999999999</v>
